--- a/data/gravel/Mondraker Arid Carbon 2025.xlsx
+++ b/data/gravel/Mondraker Arid Carbon 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B45733C-2797-3644-971D-6306A9706BA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{072CEC8B-E19A-D54F-BFC4-FF0EF7DABE15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="400" yWindow="500" windowWidth="28040" windowHeight="14560" xr2:uid="{AE0F04AA-80E5-8247-9791-D6B95FAD9AB5}"/>
+    <workbookView xWindow="760" yWindow="2220" windowWidth="28040" windowHeight="14560" xr2:uid="{AE0F04AA-80E5-8247-9791-D6B95FAD9AB5}"/>
   </bookViews>
   <sheets>
     <sheet name="Mondraker Arid Carbon 2025" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="95">
   <si>
     <t>brand</t>
   </si>
@@ -59,12 +59,6 @@
     <t>carbon</t>
   </si>
   <si>
-    <t>frame weight</t>
-  </si>
-  <si>
-    <t>UDH</t>
-  </si>
-  <si>
     <t>yes</t>
   </si>
   <si>
@@ -146,9 +140,6 @@
     <t>bb_height</t>
   </si>
   <si>
-    <t>https://whytebikes.com/products/verro-gravel-adventure-bike?variant=55457665679733</t>
-  </si>
-  <si>
     <t>Mondraker</t>
   </si>
   <si>
@@ -218,14 +209,125 @@
     <t>actual_seat_tube_angle</t>
   </si>
   <si>
-    <t>a10:g34</t>
+    <t>udh</t>
+  </si>
+  <si>
+    <t>dropout</t>
+  </si>
+  <si>
+    <t>650B tire max</t>
+  </si>
+  <si>
+    <t>suspension corrected</t>
+  </si>
+  <si>
+    <t>rear axle</t>
+  </si>
+  <si>
+    <t>front axle</t>
+  </si>
+  <si>
+    <t>q-factor</t>
+  </si>
+  <si>
+    <t>seatpost diameter</t>
+  </si>
+  <si>
+    <t>routing shifter</t>
+  </si>
+  <si>
+    <t>routing dropper</t>
+  </si>
+  <si>
+    <t>routing dynamo</t>
+  </si>
+  <si>
+    <t>front derailleur</t>
+  </si>
+  <si>
+    <t>chainring 1</t>
+  </si>
+  <si>
+    <t>chainring 2</t>
+  </si>
+  <si>
+    <t>bottom bracket</t>
+  </si>
+  <si>
+    <t>mounts inner</t>
+  </si>
+  <si>
+    <t>mounts under</t>
+  </si>
+  <si>
+    <t>mounts top</t>
+  </si>
+  <si>
+    <t>mounts fork</t>
+  </si>
+  <si>
+    <t>mounts fender rear</t>
+  </si>
+  <si>
+    <t>mounts fender front</t>
+  </si>
+  <si>
+    <t>mounts rack</t>
+  </si>
+  <si>
+    <t>rotor max front</t>
+  </si>
+  <si>
+    <t>rotor max rear</t>
+  </si>
+  <si>
+    <t>frameset</t>
+  </si>
+  <si>
+    <t>base build</t>
+  </si>
+  <si>
+    <t>currency</t>
+  </si>
+  <si>
+    <t>internal storage</t>
+  </si>
+  <si>
+    <t>T47</t>
+  </si>
+  <si>
+    <t>no</t>
+  </si>
+  <si>
+    <t>frame_weight</t>
+  </si>
+  <si>
+    <t>a10:g35</t>
+  </si>
+  <si>
+    <t>https://mondraker.com/us/en/2025-arid-carbon-rr-sl</t>
+  </si>
+  <si>
+    <t>fork suspension</t>
+  </si>
+  <si>
+    <t>stem suspension</t>
+  </si>
+  <si>
+    <t>rear suspension</t>
+  </si>
+  <si>
+    <t>700c width max</t>
+  </si>
+  <si>
+    <t>ISO ASTM</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -256,6 +358,12 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Futura"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -277,13 +385,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="15" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -618,35 +730,36 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{299AF885-3999-4E4F-8F92-5857EF0F7F08}">
-  <dimension ref="A1:R37"/>
+  <dimension ref="A1:AH37"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="36.6640625" style="1" customWidth="1"/>
-    <col min="3" max="8" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.83203125" style="1"/>
+    <col min="3" max="5" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.83203125" style="1" customWidth="1"/>
+    <col min="7" max="9" width="13.6640625" style="1" customWidth="1"/>
     <col min="10" max="10" width="19" style="1" customWidth="1"/>
     <col min="11" max="25" width="11" style="1" bestFit="1" customWidth="1"/>
     <col min="26" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -654,7 +767,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -662,64 +775,212 @@
         <v>45853</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="6" spans="1:34" customFormat="1" ht="55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="K6" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="L6" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="M6" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="N6" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="O6" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="P6" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q6" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="R6" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="S6" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="T6" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="U6" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="V6" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="W6" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="X6" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="Y6" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="Z6" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="AA6" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="AB6" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="AC6" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="AD6" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="AE6" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="AF6" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="AG6" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="AH6" s="6" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="7" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="1">
+        <v>0</v>
+      </c>
+      <c r="D7" s="1">
+        <v>50</v>
+      </c>
+      <c r="F7" s="1">
+        <v>40</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="M7" s="1">
+        <v>27.2</v>
+      </c>
+      <c r="Q7" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="R7" s="1">
+        <v>46</v>
+      </c>
+      <c r="T7" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="U7" s="1">
+        <v>2</v>
+      </c>
+      <c r="V7" s="1">
+        <v>1</v>
+      </c>
+      <c r="W7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="X7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="Y7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="Z7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE7" s="1">
+        <v>2199</v>
+      </c>
+      <c r="AF7" s="1">
+        <v>3299</v>
+      </c>
+      <c r="AH7" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C10" s="4" t="s">
+      <c r="D10" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="F10" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="G10" s="4" t="s">
         <v>40</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>43</v>
       </c>
       <c r="L10" s="3"/>
       <c r="M10" s="3"/>
@@ -729,12 +990,12 @@
       <c r="Q10" s="3"/>
       <c r="R10" s="3"/>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C11" s="5">
         <v>410</v>
@@ -760,12 +1021,12 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C12" s="5">
         <v>520</v>
@@ -791,12 +1052,12 @@
       <c r="Q12" s="3"/>
       <c r="R12" s="3"/>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C13" s="5">
         <v>75</v>
@@ -822,12 +1083,12 @@
       <c r="Q13" s="3"/>
       <c r="R13" s="3"/>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C14" s="5">
         <v>269</v>
@@ -853,12 +1114,12 @@
       <c r="Q14" s="3"/>
       <c r="R14" s="3"/>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C15" s="5">
         <v>425</v>
@@ -884,12 +1145,12 @@
       <c r="Q15" s="3"/>
       <c r="R15" s="3"/>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C16" s="5">
         <v>73</v>
@@ -917,10 +1178,10 @@
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C17" s="5">
         <v>74</v>
@@ -948,10 +1209,10 @@
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C18" s="5">
         <v>70</v>
@@ -979,10 +1240,10 @@
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C19" s="5">
         <v>45</v>
@@ -1010,10 +1271,10 @@
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C20" s="5">
         <v>1003</v>
@@ -1041,10 +1302,10 @@
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C21" s="1">
         <v>100</v>
@@ -1072,10 +1333,10 @@
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C22" s="1">
         <v>363</v>
@@ -1103,10 +1364,10 @@
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C23" s="1">
         <v>548</v>
@@ -1134,10 +1395,10 @@
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C24" s="1">
         <v>60</v>
@@ -1157,10 +1418,10 @@
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C25" s="1">
         <v>420</v>
@@ -1188,7 +1449,7 @@
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="K26" s="3"/>
       <c r="L26" s="3"/>
@@ -1201,7 +1462,7 @@
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="K27" s="3"/>
       <c r="L27" s="3"/>
@@ -1214,82 +1475,82 @@
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C30" s="1">
-        <v>700</v>
-      </c>
-      <c r="D30" s="1">
-        <v>700</v>
-      </c>
-      <c r="E30" s="1">
-        <v>700</v>
-      </c>
-      <c r="F30" s="1">
-        <v>700</v>
-      </c>
-      <c r="G30" s="1">
-        <v>700</v>
+        <v>87</v>
       </c>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C31" s="1">
-        <v>45</v>
+        <v>700</v>
       </c>
       <c r="D31" s="1">
-        <v>45</v>
+        <v>700</v>
       </c>
       <c r="E31" s="1">
-        <v>45</v>
+        <v>700</v>
       </c>
       <c r="F31" s="1">
-        <v>45</v>
+        <v>700</v>
       </c>
       <c r="G31" s="1">
-        <v>45</v>
+        <v>700</v>
       </c>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C32" s="1">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="D32" s="1">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E32" s="1">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="F32" s="1">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="G32" s="1">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
+      </c>
+      <c r="C33" s="1">
+        <v>50</v>
+      </c>
+      <c r="D33" s="1">
+        <v>50</v>
+      </c>
+      <c r="E33" s="1">
+        <v>50</v>
+      </c>
+      <c r="F33" s="1">
+        <v>50</v>
+      </c>
+      <c r="G33" s="1">
+        <v>50</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C34" s="1">
         <f>C36</f>
@@ -1300,7 +1561,7 @@
         <v>166.25</v>
       </c>
       <c r="E34" s="1">
-        <f t="shared" ref="E34:G34" si="0">AVERAGE(E36,D37)</f>
+        <f t="shared" ref="E34:F34" si="0">AVERAGE(E36,D37)</f>
         <v>175</v>
       </c>
       <c r="F34" s="1">
@@ -1308,17 +1569,20 @@
         <v>183.75</v>
       </c>
       <c r="G34" s="1">
-        <f t="shared" si="0"/>
+        <f>AVERAGE(G36,F37)</f>
         <v>191.25</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A35" s="1" t="s">
+        <v>31</v>
+      </c>
       <c r="C35" s="1">
         <f>D34</f>
         <v>166.25</v>
       </c>
       <c r="D35" s="1">
-        <f t="shared" ref="D35:F35" si="1">E34</f>
+        <f t="shared" ref="D35:E35" si="1">E34</f>
         <v>175</v>
       </c>
       <c r="E35" s="1">
@@ -1326,11 +1590,11 @@
         <v>183.75</v>
       </c>
       <c r="F35" s="1">
-        <f t="shared" si="1"/>
+        <f>G34</f>
         <v>191.25</v>
       </c>
       <c r="G35" s="1">
-        <f t="shared" ref="D34:G35" si="2">G37</f>
+        <f t="shared" ref="G35" si="2">G37</f>
         <v>200</v>
       </c>
     </row>

--- a/data/gravel/Mondraker Arid Carbon 2025.xlsx
+++ b/data/gravel/Mondraker Arid Carbon 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel copy/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B62B21F8-7403-DF41-ACF4-C068CB9B19FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5EEA2D6-D9C3-E44A-AEB2-857153665A55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="13120" windowHeight="6100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="23420" windowHeight="14400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="115">
   <si>
     <t>brand</t>
   </si>
@@ -220,9 +220,6 @@
     <t>dropout</t>
   </si>
   <si>
-    <t>0</t>
-  </si>
-  <si>
     <t>tire_width_max_700c</t>
   </si>
   <si>
@@ -365,17 +362,26 @@
   </si>
   <si>
     <t>rigid</t>
+  </si>
+  <si>
+    <t>USD</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="14"/>
       <color rgb="FF000000"/>
       <name val="Futura"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Futura"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -398,8 +404,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1253,26 +1260,26 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
+        <v>108</v>
+      </c>
+      <c r="B36" t="s">
         <v>109</v>
-      </c>
-      <c r="B36" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
+        <v>110</v>
+      </c>
+      <c r="B37" t="s">
         <v>111</v>
-      </c>
-      <c r="B37" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>112</v>
+      </c>
+      <c r="B38" t="s">
         <v>113</v>
-      </c>
-      <c r="B38" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
@@ -1295,140 +1302,128 @@
       <c r="A41" t="s">
         <v>65</v>
       </c>
-      <c r="B41" t="s">
-        <v>66</v>
-      </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
+        <v>66</v>
+      </c>
+      <c r="B42" t="s">
         <v>67</v>
-      </c>
-      <c r="B42" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
+        <v>69</v>
+      </c>
+      <c r="B44" t="s">
         <v>70</v>
-      </c>
-      <c r="B44" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>72</v>
-      </c>
-      <c r="B45" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>74</v>
-      </c>
-      <c r="B46" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>75</v>
-      </c>
-      <c r="B47" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
+        <v>77</v>
+      </c>
+      <c r="B50" t="s">
         <v>78</v>
-      </c>
-      <c r="B50" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
+        <v>80</v>
+      </c>
+      <c r="B52" t="s">
         <v>81</v>
-      </c>
-      <c r="B52" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B53" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
+        <v>83</v>
+      </c>
+      <c r="B54" t="s">
         <v>84</v>
-      </c>
-      <c r="B54" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B62" t="s">
         <v>64</v>
@@ -1436,23 +1431,23 @@
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
+        <v>93</v>
+      </c>
+      <c r="B63" t="s">
         <v>94</v>
-      </c>
-      <c r="B63" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
+        <v>95</v>
+      </c>
+      <c r="B64" t="s">
         <v>96</v>
-      </c>
-      <c r="B64" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B65" t="s">
         <v>64</v>
@@ -1460,7 +1455,7 @@
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B66" t="s">
         <v>64</v>
@@ -1468,7 +1463,7 @@
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B67" t="s">
         <v>64</v>
@@ -1476,38 +1471,41 @@
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
+        <v>102</v>
+      </c>
+      <c r="B70" t="s">
         <v>103</v>
-      </c>
-      <c r="B70" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
+        <v>104</v>
+      </c>
+      <c r="B71" t="s">
         <v>105</v>
-      </c>
-      <c r="B71" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>108</v>
+        <v>107</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>114</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Mondraker Arid Carbon 2025.xlsx
+++ b/data/gravel/Mondraker Arid Carbon 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5EEA2D6-D9C3-E44A-AEB2-857153665A55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54F1F478-6C11-BF4C-9723-E4FE936A329E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="23420" windowHeight="14400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="116">
   <si>
     <t>brand</t>
   </si>
@@ -46,9 +46,6 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://mondraker.com/us/en/2025-arid-carbon-rr-sl</t>
-  </si>
-  <si>
     <t>15-Jul-2025</t>
   </si>
   <si>
@@ -365,6 +362,12 @@
   </si>
   <si>
     <t>USD</t>
+  </si>
+  <si>
+    <t>https://mondraker.com/us/en/gravel-bikes</t>
+  </si>
+  <si>
+    <t>https://cdn.mondraker.com/storage/cache/images/426/1731509865-750_6734be69aa868888977086-arid-carbon-rr-sl-v2-p.jpg</t>
   </si>
 </sst>
 </file>
@@ -738,7 +741,7 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -746,46 +749,51 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>114</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" t="s">
         <v>10</v>
-      </c>
-      <c r="B7" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" t="s">
         <v>12</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>13</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>14</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>15</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>16</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>17</v>
-      </c>
-      <c r="G8" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" t="s">
         <v>19</v>
-      </c>
-      <c r="B9" t="s">
-        <v>20</v>
       </c>
       <c r="C9">
         <v>410</v>
@@ -805,10 +813,10 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" t="s">
         <v>21</v>
-      </c>
-      <c r="B10" t="s">
-        <v>22</v>
       </c>
       <c r="C10">
         <v>520</v>
@@ -828,10 +836,10 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" t="s">
         <v>23</v>
-      </c>
-      <c r="B11" t="s">
-        <v>24</v>
       </c>
       <c r="C11">
         <v>75</v>
@@ -851,10 +859,10 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" t="s">
         <v>25</v>
-      </c>
-      <c r="B12" t="s">
-        <v>26</v>
       </c>
       <c r="C12">
         <v>269</v>
@@ -874,10 +882,10 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" t="s">
         <v>27</v>
-      </c>
-      <c r="B13" t="s">
-        <v>28</v>
       </c>
       <c r="C13">
         <v>425</v>
@@ -897,10 +905,10 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" t="s">
         <v>29</v>
-      </c>
-      <c r="B14" t="s">
-        <v>30</v>
       </c>
       <c r="C14">
         <v>73</v>
@@ -920,10 +928,10 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15" t="s">
         <v>31</v>
-      </c>
-      <c r="B15" t="s">
-        <v>32</v>
       </c>
       <c r="C15">
         <v>74</v>
@@ -943,10 +951,10 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
+        <v>32</v>
+      </c>
+      <c r="B16" t="s">
         <v>33</v>
-      </c>
-      <c r="B16" t="s">
-        <v>34</v>
       </c>
       <c r="C16">
         <v>70</v>
@@ -966,10 +974,10 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
+        <v>34</v>
+      </c>
+      <c r="B17" t="s">
         <v>35</v>
-      </c>
-      <c r="B17" t="s">
-        <v>36</v>
       </c>
       <c r="C17">
         <v>45</v>
@@ -989,10 +997,10 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
+        <v>36</v>
+      </c>
+      <c r="B18" t="s">
         <v>37</v>
-      </c>
-      <c r="B18" t="s">
-        <v>38</v>
       </c>
       <c r="C18">
         <v>1003</v>
@@ -1012,10 +1020,10 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
+        <v>38</v>
+      </c>
+      <c r="B19" t="s">
         <v>39</v>
-      </c>
-      <c r="B19" t="s">
-        <v>40</v>
       </c>
       <c r="C19">
         <v>100</v>
@@ -1035,10 +1043,10 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" t="s">
         <v>41</v>
-      </c>
-      <c r="B20" t="s">
-        <v>42</v>
       </c>
       <c r="C20">
         <v>363</v>
@@ -1058,10 +1066,10 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
+        <v>42</v>
+      </c>
+      <c r="B21" t="s">
         <v>43</v>
-      </c>
-      <c r="B21" t="s">
-        <v>44</v>
       </c>
       <c r="C21">
         <v>548</v>
@@ -1081,10 +1089,10 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
+        <v>44</v>
+      </c>
+      <c r="B22" t="s">
         <v>45</v>
-      </c>
-      <c r="B22" t="s">
-        <v>46</v>
       </c>
       <c r="C22">
         <v>60</v>
@@ -1104,10 +1112,10 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
+        <v>46</v>
+      </c>
+      <c r="B23" t="s">
         <v>47</v>
-      </c>
-      <c r="B23" t="s">
-        <v>48</v>
       </c>
       <c r="C23">
         <v>420</v>
@@ -1127,32 +1135,32 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C29">
         <v>700</v>
@@ -1172,7 +1180,7 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C30">
         <v>45</v>
@@ -1192,7 +1200,7 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C31">
         <v>50</v>
@@ -1212,7 +1220,7 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C32">
         <v>160</v>
@@ -1232,7 +1240,7 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C33">
         <v>166.25</v>
@@ -1252,260 +1260,260 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
+        <v>58</v>
+      </c>
+      <c r="B35" t="s">
         <v>59</v>
-      </c>
-      <c r="B35" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
+        <v>107</v>
+      </c>
+      <c r="B36" t="s">
         <v>108</v>
-      </c>
-      <c r="B36" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
+        <v>109</v>
+      </c>
+      <c r="B37" t="s">
         <v>110</v>
-      </c>
-      <c r="B37" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>111</v>
+      </c>
+      <c r="B38" t="s">
         <v>112</v>
-      </c>
-      <c r="B38" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
+        <v>60</v>
+      </c>
+      <c r="B39" t="s">
         <v>61</v>
-      </c>
-      <c r="B39" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
+        <v>62</v>
+      </c>
+      <c r="B40" t="s">
         <v>63</v>
-      </c>
-      <c r="B40" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
+        <v>65</v>
+      </c>
+      <c r="B42" t="s">
         <v>66</v>
-      </c>
-      <c r="B42" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
+        <v>68</v>
+      </c>
+      <c r="B44" t="s">
         <v>69</v>
-      </c>
-      <c r="B44" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
+        <v>76</v>
+      </c>
+      <c r="B50" t="s">
         <v>77</v>
-      </c>
-      <c r="B50" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
+        <v>79</v>
+      </c>
+      <c r="B52" t="s">
         <v>80</v>
-      </c>
-      <c r="B52" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B53" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
+        <v>82</v>
+      </c>
+      <c r="B54" t="s">
         <v>83</v>
-      </c>
-      <c r="B54" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B62" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
+        <v>92</v>
+      </c>
+      <c r="B63" t="s">
         <v>93</v>
-      </c>
-      <c r="B63" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
+        <v>94</v>
+      </c>
+      <c r="B64" t="s">
         <v>95</v>
-      </c>
-      <c r="B64" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B65" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B66" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B67" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
+        <v>101</v>
+      </c>
+      <c r="B70" t="s">
         <v>102</v>
-      </c>
-      <c r="B70" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
+        <v>103</v>
+      </c>
+      <c r="B71" t="s">
         <v>104</v>
-      </c>
-      <c r="B71" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Mondraker Arid Carbon 2025.xlsx
+++ b/data/gravel/Mondraker Arid Carbon 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54F1F478-6C11-BF4C-9723-E4FE936A329E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4AD7592-53BF-FC4E-976D-38C8BF04CE6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="23420" windowHeight="14400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="118">
   <si>
     <t>brand</t>
   </si>
@@ -368,6 +368,12 @@
   </si>
   <si>
     <t>https://cdn.mondraker.com/storage/cache/images/426/1731509865-750_6734be69aa868888977086-arid-carbon-rr-sl-v2-p.jpg</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Elche, Alicante, Spain</t>
   </si>
 </sst>
 </file>
@@ -706,7 +712,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G73"/>
+  <dimension ref="A1:G74"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1516,6 +1522,14 @@
         <v>113</v>
       </c>
     </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>116</v>
+      </c>
+      <c r="B74" t="s">
+        <v>117</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/data/gravel/Mondraker Arid Carbon 2025.xlsx
+++ b/data/gravel/Mondraker Arid Carbon 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4AD7592-53BF-FC4E-976D-38C8BF04CE6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6330F141-84DE-964A-8804-8B8C10DB34EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="23420" windowHeight="14400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4160" yWindow="600" windowWidth="23420" windowHeight="14400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="119">
   <si>
     <t>brand</t>
   </si>
@@ -374,6 +374,9 @@
   </si>
   <si>
     <t>Elche, Alicante, Spain</t>
+  </si>
+  <si>
+    <t>internal</t>
   </si>
 </sst>
 </file>
@@ -1429,6 +1432,9 @@
       <c r="A60" t="s">
         <v>89</v>
       </c>
+      <c r="B60" s="1" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">

--- a/data/gravel/Mondraker Arid Carbon 2025.xlsx
+++ b/data/gravel/Mondraker Arid Carbon 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6330F141-84DE-964A-8804-8B8C10DB34EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89B11438-ADA9-1346-A7FF-7EA3B0274657}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4160" yWindow="600" windowWidth="23420" windowHeight="14400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="125">
   <si>
     <t>brand</t>
   </si>
@@ -377,6 +377,24 @@
   </si>
   <si>
     <t>internal</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -715,7 +733,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G74"/>
+  <dimension ref="A1:G80"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1368,171 +1386,201 @@
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>76</v>
-      </c>
-      <c r="B50" t="s">
-        <v>77</v>
+        <v>119</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>78</v>
+        <v>120</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>79</v>
-      </c>
-      <c r="B52" t="s">
-        <v>80</v>
+        <v>121</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>81</v>
-      </c>
-      <c r="B53" t="s">
-        <v>71</v>
+        <v>122</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>82</v>
-      </c>
-      <c r="B54" t="s">
-        <v>83</v>
+        <v>123</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>84</v>
+        <v>124</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>85</v>
+        <v>76</v>
+      </c>
+      <c r="B56" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>87</v>
+        <v>79</v>
+      </c>
+      <c r="B58" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>88</v>
+        <v>81</v>
+      </c>
+      <c r="B59" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>89</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>118</v>
+        <v>82</v>
+      </c>
+      <c r="B60" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>91</v>
-      </c>
-      <c r="B62" t="s">
-        <v>63</v>
+        <v>85</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>92</v>
-      </c>
-      <c r="B63" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>94</v>
-      </c>
-      <c r="B64" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>96</v>
-      </c>
-      <c r="B65" t="s">
-        <v>63</v>
+        <v>88</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>97</v>
-      </c>
-      <c r="B66" t="s">
-        <v>63</v>
+        <v>89</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>98</v>
-      </c>
-      <c r="B67" t="s">
-        <v>63</v>
+        <v>90</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>99</v>
+        <v>91</v>
+      </c>
+      <c r="B68" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>100</v>
+        <v>92</v>
+      </c>
+      <c r="B69" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="B70" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="B71" t="s">
-        <v>104</v>
+        <v>63</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>105</v>
+        <v>97</v>
+      </c>
+      <c r="B72" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>106</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>113</v>
+        <v>98</v>
+      </c>
+      <c r="B73" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>101</v>
+      </c>
+      <c r="B76" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>103</v>
+      </c>
+      <c r="B77" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>106</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
         <v>116</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B80" t="s">
         <v>117</v>
       </c>
     </row>
